--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="511">
   <si>
     <t/>
   </si>
@@ -127,7 +127,7 @@
     <t>20138228</t>
   </si>
   <si>
-    <t>LAYS RUMPUT LAUT 64G</t>
+    <t>LAYS RMPT LAUT 64 G</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -136,13 +136,13 @@
     <t>20138229</t>
   </si>
   <si>
-    <t>LAYS DGG SAPI BKR64G</t>
+    <t>LAYS SAPI BKR 64 G</t>
   </si>
   <si>
     <t>20141504</t>
   </si>
   <si>
-    <t>LAYS RMPT LAUT PDS64</t>
+    <t>LAYS R.LAUT PDS 64 G</t>
   </si>
   <si>
     <t>20116670</t>
@@ -163,12 +163,6 @@
     <t>CHITATO BEEF MALA 65</t>
   </si>
   <si>
-    <t>20136744</t>
-  </si>
-  <si>
-    <t>CHITATO TTEOK-BK 65G</t>
-  </si>
-  <si>
     <t>20141944</t>
   </si>
   <si>
@@ -307,19 +301,19 @@
     <t>20136007</t>
   </si>
   <si>
-    <t>MR.POTATO BBQ 85G</t>
+    <t>MR.POTATO BBQ 85 G</t>
   </si>
   <si>
     <t>20135539</t>
   </si>
   <si>
-    <t>MR.POTATO ORGINAL85G</t>
+    <t>MR.POTATO ORI 85 G</t>
   </si>
   <si>
     <t>20135538</t>
   </si>
   <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
+    <t>MR.POTATO S&amp;O 85 G</t>
   </si>
   <si>
     <t>20137054</t>
@@ -376,12 +370,6 @@
     <t>KUSUKA RMPT LAUT 60</t>
   </si>
   <si>
-    <t>20012678</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK ORG 60</t>
-  </si>
-  <si>
     <t>20012679</t>
   </si>
   <si>
@@ -445,7 +433,7 @@
     <t>20115362</t>
   </si>
   <si>
-    <t>CHUBA KRP BALADO 120</t>
+    <t>CHUBA KRP BLDO 120 G</t>
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
@@ -454,13 +442,13 @@
     <t>20115363</t>
   </si>
   <si>
-    <t>CHUBA KRPK BBQ 120G</t>
+    <t>CHUBA KRP BBQ 120 G</t>
   </si>
   <si>
     <t>20137973</t>
   </si>
   <si>
-    <t>CHUBA KRIPIK KEJU120</t>
+    <t>CHUBA KRP KEJU 120 G</t>
   </si>
   <si>
     <t>20000516</t>
@@ -505,10 +493,10 @@
     <t>QTELA KR AY LD/HT100</t>
   </si>
   <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
+    <t>20143944</t>
+  </si>
+  <si>
+    <t>PTOS KRN HNY BTR105</t>
   </si>
   <si>
     <t>12</t>
@@ -643,21 +631,15 @@
     <t>WONHAE BANANA MB 60G</t>
   </si>
   <si>
-    <t>20116109</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 55G</t>
+    <t>20083529</t>
+  </si>
+  <si>
+    <t>HAPPY TOS SEAWEED 52</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20083529</t>
-  </si>
-  <si>
-    <t>HAPPY TOS SEAWEED 52</t>
-  </si>
-  <si>
     <t>20037179</t>
   </si>
   <si>
@@ -1378,6 +1360,12 @@
     <t>IDM KACANG KULIT 180</t>
   </si>
   <si>
+    <t>20143897</t>
+  </si>
+  <si>
+    <t>GARUDA KCG TLR BLD90</t>
+  </si>
+  <si>
     <t>10026501</t>
   </si>
   <si>
@@ -1438,12 +1426,6 @@
     <t>SUKRO KC OVEN BWG 95</t>
   </si>
   <si>
-    <t>20139132</t>
-  </si>
-  <si>
-    <t>GRUDA RS.MAX B&amp;S 80G</t>
-  </si>
-  <si>
     <t>20120796</t>
   </si>
   <si>
@@ -1462,19 +1444,13 @@
     <t>GRUDA K.ATOM PDS 220</t>
   </si>
   <si>
-    <t>20137700</t>
-  </si>
-  <si>
-    <t>MAYASI CSHW KTCY 35G</t>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
   </si>
   <si>
     <t>37</t>
-  </si>
-  <si>
-    <t>20052766</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE MDU 80</t>
   </si>
   <si>
     <t>20096682</t>
@@ -1960,7 +1936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F236"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2384,7 +2360,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -2401,10 +2377,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -2424,7 +2400,7 @@
         <v>26</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>9</v>
@@ -2444,7 +2420,7 @@
         <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>9</v>
@@ -2464,7 +2440,7 @@
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>9</v>
@@ -2484,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>9</v>
@@ -2504,7 +2480,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>9</v>
@@ -2521,13 +2497,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,7 +2520,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>39</v>
@@ -2564,7 +2540,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>39</v>
@@ -2584,7 +2560,7 @@
         <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>39</v>
@@ -2604,7 +2580,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>39</v>
@@ -2624,7 +2600,7 @@
         <v>29</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>39</v>
@@ -2644,7 +2620,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>39</v>
@@ -2652,10 +2628,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2664,7 +2640,7 @@
         <v>29</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>39</v>
@@ -2672,10 +2648,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2684,30 +2660,30 @@
         <v>29</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2721,10 +2697,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>39</v>
@@ -2741,10 +2717,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>39</v>
@@ -2761,33 +2737,33 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,10 +2777,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>39</v>
@@ -2821,10 +2797,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>39</v>
@@ -2841,13 +2817,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2861,10 +2837,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>9</v>
@@ -2881,10 +2857,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2892,19 +2868,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2912,22 +2888,22 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2941,13 +2917,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,10 +2937,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>30</v>
@@ -2981,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>30</v>
@@ -3001,13 +2977,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,10 +2997,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>9</v>
@@ -3041,13 +3017,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3061,13 +3037,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,13 +3057,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3101,133 +3077,133 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,13 +3217,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3261,13 +3237,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,13 +3257,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,13 +3277,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3321,10 +3297,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>9</v>
@@ -3341,10 +3317,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -3361,10 +3337,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>9</v>
@@ -3381,50 +3357,50 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>39</v>
@@ -3441,10 +3417,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>30</v>
@@ -3461,13 +3437,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,50 +3457,50 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>9</v>
@@ -3541,13 +3517,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,13 +3537,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,10 +3557,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>9</v>
@@ -3592,39 +3568,39 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>9</v>
@@ -3641,13 +3617,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3661,13 +3637,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,10 +3657,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>39</v>
@@ -3701,10 +3677,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>39</v>
@@ -3712,19 +3688,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>39</v>
@@ -3732,22 +3708,22 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3761,10 +3737,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>39</v>
@@ -3781,13 +3757,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,10 +3777,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>39</v>
@@ -3812,39 +3788,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>9</v>
@@ -3861,10 +3837,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>39</v>
@@ -3881,13 +3857,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3901,30 +3877,30 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>39</v>
@@ -3932,19 +3908,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>39</v>
@@ -3952,19 +3928,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>39</v>
@@ -3981,13 +3957,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4001,73 +3977,73 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4081,13 +4057,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,13 +4077,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4121,73 +4097,73 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,13 +4177,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4221,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>9</v>
@@ -4232,59 +4208,59 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>9</v>
@@ -4301,13 +4277,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4321,50 +4297,50 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>39</v>
@@ -4372,22 +4348,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4401,10 +4377,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>39</v>
@@ -4421,10 +4397,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>39</v>
@@ -4441,30 +4417,30 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>39</v>
@@ -4472,39 +4448,39 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>39</v>
@@ -4521,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>39</v>
@@ -4532,59 +4508,59 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>39</v>
@@ -4601,10 +4577,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>39</v>
@@ -4621,30 +4597,30 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>39</v>
@@ -4652,19 +4628,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>39</v>
@@ -4672,19 +4648,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>39</v>
@@ -4701,10 +4677,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>39</v>
@@ -4721,10 +4697,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>39</v>
@@ -4732,19 +4708,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>39</v>
@@ -4752,42 +4728,42 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,13 +4777,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4821,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>30</v>
@@ -4832,62 +4808,62 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4901,13 +4877,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4921,10 +4897,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>39</v>
@@ -4941,13 +4917,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,73 +4937,73 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5041,13 +5017,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5061,10 +5037,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>30</v>
@@ -5081,13 +5057,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5101,73 +5077,73 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,13 +5157,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5201,13 +5177,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5221,70 +5197,70 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -5301,10 +5277,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5321,13 +5297,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5341,50 +5317,50 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>30</v>
@@ -5392,22 +5368,22 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5421,13 +5397,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5441,10 +5417,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>30</v>
@@ -5461,70 +5437,70 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>39</v>
@@ -5541,10 +5517,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>39</v>
@@ -5561,10 +5537,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>39</v>
@@ -5581,10 +5557,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>39</v>
@@ -5601,10 +5577,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>39</v>
@@ -5621,10 +5597,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>39</v>
@@ -5641,10 +5617,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>39</v>
@@ -5652,19 +5628,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>39</v>
@@ -5672,42 +5648,42 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5721,13 +5697,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5741,13 +5717,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,13 +5737,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5781,13 +5757,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5801,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>39</v>
@@ -5812,19 +5788,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>39</v>
@@ -5832,19 +5808,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>39</v>
@@ -5852,19 +5828,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>39</v>
@@ -5881,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>39</v>
@@ -5901,10 +5877,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>39</v>
@@ -5921,10 +5897,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>39</v>
@@ -5941,10 +5917,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>39</v>
@@ -5952,19 +5928,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>39</v>
@@ -5972,19 +5948,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>39</v>
@@ -5992,19 +5968,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>39</v>
@@ -6021,13 +5997,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6041,10 +6017,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>39</v>
@@ -6061,10 +6037,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>39</v>
@@ -6072,39 +6048,39 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>39</v>
@@ -6121,10 +6097,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>39</v>
@@ -6141,10 +6117,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>39</v>
@@ -6161,10 +6137,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>39</v>
@@ -6181,10 +6157,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>39</v>
@@ -6201,10 +6177,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>39</v>
@@ -6212,19 +6188,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>39</v>
@@ -6232,19 +6208,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>39</v>
@@ -6261,10 +6237,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>39</v>
@@ -6281,10 +6257,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>39</v>
@@ -6301,73 +6277,73 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6381,13 +6357,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6401,13 +6377,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6421,13 +6397,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6461,13 +6437,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6481,50 +6457,50 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>39</v>
@@ -6532,19 +6508,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>39</v>
@@ -6552,22 +6528,22 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6581,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6601,92 +6577,12 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E233" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F235" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F236" s="1" t="s">
         <v>39</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
   <si>
     <t/>
   </si>
@@ -109,19 +109,19 @@
     <t>20132750</t>
   </si>
   <si>
-    <t>CHITATO AYAM BWG 65G</t>
+    <t>CHTT LT SP A BW 65 G</t>
   </si>
   <si>
     <t>20116686</t>
   </si>
   <si>
-    <t>C/LITE SRCRM ONION65</t>
+    <t>CHTATO LT SP SO 68 G</t>
   </si>
   <si>
     <t>20131037</t>
   </si>
   <si>
-    <t>CHTATOLITE ABR.SWD65</t>
+    <t>CHTATO LT SP AS 65 G</t>
   </si>
   <si>
     <t>20138228</t>
@@ -148,61 +148,61 @@
     <t>20116670</t>
   </si>
   <si>
-    <t>CHTATO LITE NORI 65G</t>
+    <t>CHTATO LT SP NR 65 G</t>
   </si>
   <si>
     <t>20116684</t>
   </si>
   <si>
-    <t>C/LITE SLMON TRYKI65</t>
+    <t>CHTATO LT SP ST 68 G</t>
   </si>
   <si>
     <t>20139713</t>
   </si>
   <si>
-    <t>CHITATO BEEF MALA 65</t>
+    <t>CHITATO BF MALA 65 G</t>
   </si>
   <si>
     <t>20141944</t>
   </si>
   <si>
-    <t>CHITATO RNDG SAPI 62</t>
+    <t>CHITATO RD SAPI 62 G</t>
   </si>
   <si>
     <t>10001094</t>
   </si>
   <si>
-    <t>CHITATO SAPI PGG 65G</t>
+    <t>CHITATO SAPI PG 65 G</t>
   </si>
   <si>
     <t>20122264</t>
   </si>
   <si>
-    <t>CHITATO MI GORENG 65</t>
+    <t>CHITATO MI GRNG 65 G</t>
   </si>
   <si>
     <t>10001093</t>
   </si>
   <si>
-    <t>CHITATO AYAM BMB 65G</t>
+    <t>CHITATO AY BMB 65 G</t>
   </si>
   <si>
     <t>20014506</t>
   </si>
   <si>
-    <t>CHITATO CHEESE SPR65</t>
+    <t>CHITATO CHE.SUP 65 G</t>
   </si>
   <si>
     <t>20023435</t>
   </si>
   <si>
-    <t>CHITATO SP BMB BKR65</t>
+    <t>CHITATO SP B.BK 65 G</t>
   </si>
   <si>
     <t>20029228</t>
   </si>
   <si>
-    <t>CHITATO AYAM BBQ 65G</t>
+    <t>CHITATO AY BBQ 65 G</t>
   </si>
   <si>
     <t>20052859</t>
@@ -664,10 +664,16 @@
     <t>TOS TOS TRTCS KB140</t>
   </si>
   <si>
+    <t>20144171</t>
+  </si>
+  <si>
+    <t>KRISBEE CHCKN NGT75G</t>
+  </si>
+  <si>
     <t>20138231</t>
   </si>
   <si>
-    <t>DORITOS SMB SALSA120</t>
+    <t>DORITOS S SLSA 120 G</t>
   </si>
   <si>
     <t>17</t>
@@ -676,13 +682,13 @@
     <t>20138230</t>
   </si>
   <si>
-    <t>DORITOS JGG BKR 120G</t>
+    <t>DORITOS JG BKR 120 G</t>
   </si>
   <si>
     <t>20142266</t>
   </si>
   <si>
-    <t>DORITOS NCHO CHS 120</t>
+    <t>DORITOS N.CH 120 G</t>
   </si>
   <si>
     <t>20131013</t>
@@ -841,15 +847,27 @@
     <t>STT FRCH FRS LVL3 60</t>
   </si>
   <si>
+    <t>20138235</t>
+  </si>
+  <si>
+    <t>CHEETOS KEJU 68G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20138234</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 68G</t>
+  </si>
+  <si>
     <t>20034682</t>
   </si>
   <si>
     <t>RIN-BEE STICK KEJU60</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>20057730</t>
   </si>
   <si>
@@ -871,7 +889,7 @@
     <t>20138241</t>
   </si>
   <si>
-    <t>CHEETOS KEJU 120G</t>
+    <t>CHEETOS KEJU 120 G</t>
   </si>
   <si>
     <t>23</t>
@@ -880,7 +898,7 @@
     <t>20143053</t>
   </si>
   <si>
-    <t>CETOS SWTS KJ MNS120</t>
+    <t>CHEETOS S K.MS 120 G</t>
   </si>
   <si>
     <t>20140272</t>
@@ -904,7 +922,7 @@
     <t>20138236</t>
   </si>
   <si>
-    <t>CHEETOS JGG BKR 120G</t>
+    <t>CHEETOS JG BKR 120 G</t>
   </si>
   <si>
     <t>24</t>
@@ -1447,7 +1465,7 @@
     <t>20052766</t>
   </si>
   <si>
-    <t>IDM KCNG METE MDU 80</t>
+    <t>IDM KCNG METE MDU 65</t>
   </si>
   <si>
     <t>37</t>
@@ -1936,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F232"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3780,7 +3798,7 @@
         <v>208</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>39</v>
@@ -3800,7 +3818,7 @@
         <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>30</v>
@@ -3820,7 +3838,7 @@
         <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>9</v>
@@ -3840,7 +3858,7 @@
         <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>39</v>
@@ -3860,7 +3878,7 @@
         <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>39</v>
@@ -3877,10 +3895,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>39</v>
@@ -3888,19 +3906,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>39</v>
@@ -3917,10 +3935,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>39</v>
@@ -3937,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>39</v>
@@ -3957,13 +3975,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3977,30 +3995,30 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>131</v>
@@ -4017,13 +4035,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4037,10 +4055,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>39</v>
@@ -4057,13 +4075,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4077,10 +4095,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>30</v>
@@ -4097,30 +4115,30 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>9</v>
@@ -4137,10 +4155,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>9</v>
@@ -4157,13 +4175,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,10 +4195,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>30</v>
@@ -4197,30 +4215,30 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>9</v>
@@ -4237,10 +4255,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>9</v>
@@ -4257,10 +4275,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>9</v>
@@ -4277,13 +4295,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,10 +4315,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>39</v>
@@ -4308,19 +4326,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>39</v>
@@ -4337,10 +4355,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>39</v>
@@ -4357,13 +4375,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4377,13 +4395,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4397,10 +4415,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>39</v>
@@ -4417,10 +4435,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>39</v>
@@ -4428,19 +4446,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>39</v>
@@ -4457,13 +4475,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4477,10 +4495,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>39</v>
@@ -4497,10 +4515,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>39</v>
@@ -4508,59 +4526,59 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>39</v>
@@ -4577,10 +4595,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>39</v>
@@ -4597,30 +4615,30 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>39</v>
@@ -4628,19 +4646,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>39</v>
@@ -4648,19 +4666,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>39</v>
@@ -4677,10 +4695,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>39</v>
@@ -4697,10 +4715,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>39</v>
@@ -4708,19 +4726,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>39</v>
@@ -4728,42 +4746,42 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,13 +4795,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4797,10 +4815,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>30</v>
@@ -4808,62 +4826,62 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4877,13 +4895,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4897,10 +4915,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>39</v>
@@ -4917,13 +4935,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4937,73 +4955,73 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5017,13 +5035,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5037,10 +5055,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>30</v>
@@ -5057,13 +5075,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5077,73 +5095,73 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5157,13 +5175,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5177,13 +5195,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,70 +5215,70 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -5277,10 +5295,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5297,13 +5315,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5317,50 +5335,50 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>30</v>
@@ -5368,22 +5386,22 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5397,13 +5415,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5417,10 +5435,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>30</v>
@@ -5437,70 +5455,70 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>39</v>
@@ -5517,10 +5535,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>39</v>
@@ -5537,10 +5555,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>39</v>
@@ -5557,10 +5575,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>39</v>
@@ -5577,10 +5595,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>39</v>
@@ -5597,10 +5615,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>39</v>
@@ -5617,10 +5635,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>39</v>
@@ -5628,19 +5646,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>39</v>
@@ -5648,42 +5666,42 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5697,13 +5715,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5717,13 +5735,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5737,13 +5755,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5757,13 +5775,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5777,10 +5795,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>39</v>
@@ -5788,19 +5806,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>39</v>
@@ -5808,19 +5826,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>39</v>
@@ -5828,19 +5846,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>39</v>
@@ -5857,10 +5875,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>39</v>
@@ -5877,10 +5895,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>39</v>
@@ -5897,10 +5915,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>39</v>
@@ -5917,10 +5935,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>39</v>
@@ -5928,19 +5946,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>39</v>
@@ -5948,19 +5966,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>39</v>
@@ -5968,19 +5986,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>39</v>
@@ -5997,13 +6015,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6017,10 +6035,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>39</v>
@@ -6037,10 +6055,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>39</v>
@@ -6048,39 +6066,39 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>39</v>
@@ -6088,19 +6106,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>39</v>
@@ -6117,10 +6135,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>39</v>
@@ -6137,10 +6155,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>39</v>
@@ -6157,10 +6175,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>39</v>
@@ -6177,10 +6195,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>39</v>
@@ -6188,19 +6206,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>39</v>
@@ -6208,19 +6226,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>39</v>
@@ -6228,19 +6246,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>39</v>
@@ -6257,10 +6275,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>39</v>
@@ -6277,70 +6295,70 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>85</v>
@@ -6357,10 +6375,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>85</v>
@@ -6377,13 +6395,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,10 +6415,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>85</v>
@@ -6417,13 +6435,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,13 +6455,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,10 +6475,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>85</v>
@@ -6468,39 +6486,39 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>39</v>
@@ -6508,22 +6526,22 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6537,13 +6555,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,10 +6575,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>39</v>
@@ -6577,12 +6595,72 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E232" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F232" s="1" t="s">
+      <c r="F235" s="1" t="s">
         <v>39</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
   <si>
     <t/>
   </si>
@@ -70,25 +70,25 @@
     <t>20131098</t>
   </si>
   <si>
-    <t>POTABEE SPICY BBQ 65</t>
+    <t>POTABE SPCY BBQ 65 G</t>
   </si>
   <si>
     <t>20093941</t>
   </si>
   <si>
-    <t>POTABEE AYM BKR 65G</t>
+    <t>POTABE AYM BKR 65 G</t>
   </si>
   <si>
     <t>20071780</t>
   </si>
   <si>
-    <t>POTABEE CHIP BBQ 65G</t>
+    <t>POTABE CHIP BBQ 65 G</t>
   </si>
   <si>
     <t>20071781</t>
   </si>
   <si>
-    <t>POTABEE CHIP SWD 65G</t>
+    <t>POTABE CHIP SWD 65 G</t>
   </si>
   <si>
     <t>5</t>
@@ -199,12 +199,6 @@
     <t>CHITATO SP B.BK 65 G</t>
   </si>
   <si>
-    <t>20029228</t>
-  </si>
-  <si>
-    <t>CHITATO AY BBQ 65 G</t>
-  </si>
-  <si>
     <t>20052859</t>
   </si>
   <si>
@@ -655,13 +649,13 @@
     <t>20130447</t>
   </si>
   <si>
-    <t>TOS TOS TRTCS RC140</t>
+    <t>TSTS TRTL CHP R/C130</t>
   </si>
   <si>
     <t>20128517</t>
   </si>
   <si>
-    <t>TOS TOS TRTCS KB140</t>
+    <t>TSTS TRTL CHP K/B130</t>
   </si>
   <si>
     <t>20144171</t>
@@ -706,7 +700,7 @@
     <t>20072195</t>
   </si>
   <si>
-    <t>MH MAITOS JG.BBQ 120</t>
+    <t>MAITOS JG BBQ 140 G</t>
   </si>
   <si>
     <t>18</t>
@@ -715,7 +709,7 @@
     <t>20072194</t>
   </si>
   <si>
-    <t>MH MAITOS S.BLDO 120</t>
+    <t>MAITOS S.BLDO 140 G</t>
   </si>
   <si>
     <t>20099956</t>
@@ -766,7 +760,7 @@
     <t>10002101</t>
   </si>
   <si>
-    <t>HAPPYTOS CHIP MRH140</t>
+    <t>HAPPYTOS CHP M 140 G</t>
   </si>
   <si>
     <t>20119019</t>
@@ -1111,13 +1105,13 @@
     <t>20132871</t>
   </si>
   <si>
-    <t>DK RONI RS.CORN 135G</t>
+    <t>DK RONI RS.CORN 130G</t>
   </si>
   <si>
     <t>20114756</t>
   </si>
   <si>
-    <t>GURIBEE BBQ BLDO 62G</t>
+    <t>GURIBEE BBQ BLD 65 G</t>
   </si>
   <si>
     <t>29</t>
@@ -1126,13 +1120,13 @@
     <t>20114757</t>
   </si>
   <si>
-    <t>GURIBEE RMP.LAUT 62G</t>
+    <t>GURIBEE R.LAUT 65 G</t>
   </si>
   <si>
     <t>20130511</t>
   </si>
   <si>
-    <t>GURIBEE KEJU 62G</t>
+    <t>GURIBEE KEJU 65 G</t>
   </si>
   <si>
     <t>20141505</t>
@@ -1267,7 +1261,7 @@
     <t>20036562</t>
   </si>
   <si>
-    <t>S/N SOSIS AYAM 500</t>
+    <t>S/N SOSIS AYAM 432G</t>
   </si>
   <si>
     <t>10024188</t>
@@ -1387,7 +1381,7 @@
     <t>10026501</t>
   </si>
   <si>
-    <t>DK KACANG SUKRO 95G</t>
+    <t>DK KACANG SUKRO 95 G</t>
   </si>
   <si>
     <t>35</t>
@@ -1408,19 +1402,19 @@
     <t>10003840</t>
   </si>
   <si>
-    <t>GARUDA KCG.TELUR 100</t>
+    <t>GARUDA KC.TLR 110 G</t>
   </si>
   <si>
     <t>20136516</t>
   </si>
   <si>
-    <t>IDM KC ATM CB IJO120</t>
+    <t>IDM K AT C.IJO 120 G</t>
   </si>
   <si>
     <t>20042632</t>
   </si>
   <si>
-    <t>IDM KCG ATOM PDS 140</t>
+    <t>IDM K ATOM PDS 140 G</t>
   </si>
   <si>
     <t>20072370</t>
@@ -1432,7 +1426,7 @@
     <t>20062966</t>
   </si>
   <si>
-    <t>DK SUKRO BBQ 95G</t>
+    <t>DK SUKRO BBQ 95 G</t>
   </si>
   <si>
     <t>36</t>
@@ -1441,7 +1435,7 @@
     <t>20084707</t>
   </si>
   <si>
-    <t>SUKRO KC OVEN BWG 95</t>
+    <t>DK SUKRO OV BWG 95 G</t>
   </si>
   <si>
     <t>20120796</t>
@@ -1474,7 +1468,7 @@
     <t>20096682</t>
   </si>
   <si>
-    <t>IDM KACANG JUMBO 80</t>
+    <t>IDM K JUMBO 80 G</t>
   </si>
   <si>
     <t>20066374</t>
@@ -1492,13 +1486,13 @@
     <t>20139150</t>
   </si>
   <si>
-    <t>IDM KCNG KORO BLD 80</t>
+    <t>IDM KC KORO BLD 80 G</t>
   </si>
   <si>
     <t>10003507</t>
   </si>
   <si>
-    <t>MR.P KACANG MADU 80G</t>
+    <t>MR.P KCANG MADU 80 G</t>
   </si>
   <si>
     <t>20047037</t>
@@ -1954,7 +1948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2495,13 +2489,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2518,7 +2512,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>39</v>
@@ -2538,7 +2532,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>39</v>
@@ -2558,7 +2552,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>39</v>
@@ -2578,7 +2572,7 @@
         <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>39</v>
@@ -2598,7 +2592,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>39</v>
@@ -2618,7 +2612,7 @@
         <v>29</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>39</v>
@@ -2626,10 +2620,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2638,7 +2632,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>39</v>
@@ -2646,10 +2640,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2658,30 +2652,30 @@
         <v>29</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>39</v>
@@ -2715,10 +2709,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>39</v>
@@ -2735,33 +2729,33 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,10 +2769,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>39</v>
@@ -2795,10 +2789,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>39</v>
@@ -2815,13 +2809,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,10 +2829,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>9</v>
@@ -2855,10 +2849,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>9</v>
@@ -2866,19 +2860,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2886,22 +2880,22 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2915,13 +2909,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,10 +2929,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>30</v>
@@ -2955,10 +2949,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>30</v>
@@ -2975,13 +2969,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2995,10 +2989,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>9</v>
@@ -3015,13 +3009,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3035,13 +3029,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3055,10 +3049,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>39</v>
@@ -3075,33 +3069,33 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3115,33 +3109,33 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3155,33 +3149,33 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3195,13 +3189,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,13 +3209,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,10 +3229,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>30</v>
@@ -3255,13 +3249,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,10 +3269,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>9</v>
@@ -3295,10 +3289,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>9</v>
@@ -3315,10 +3309,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>9</v>
@@ -3335,10 +3329,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -3355,33 +3349,33 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,13 +3389,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,13 +3409,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,13 +3429,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,33 +3449,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,13 +3489,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3515,10 +3509,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>9</v>
@@ -3535,13 +3529,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3555,30 +3549,30 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>9</v>
@@ -3595,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>9</v>
@@ -3615,13 +3609,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3635,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>39</v>
@@ -3655,10 +3649,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>39</v>
@@ -3675,10 +3669,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>39</v>
@@ -3686,19 +3680,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>39</v>
@@ -3715,13 +3709,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,13 +3729,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,10 +3749,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>39</v>
@@ -3775,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>39</v>
@@ -3786,22 +3780,22 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,13 +3809,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,13 +3829,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3855,10 +3849,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>39</v>
@@ -3875,10 +3869,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>39</v>
@@ -3895,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>39</v>
@@ -3906,19 +3900,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>39</v>
@@ -3935,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>39</v>
@@ -3955,10 +3949,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>39</v>
@@ -3975,13 +3969,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,33 +3989,33 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4035,13 +4029,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,10 +4049,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>39</v>
@@ -4075,13 +4069,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,10 +4089,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>30</v>
@@ -4115,30 +4109,30 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>9</v>
@@ -4155,10 +4149,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>9</v>
@@ -4175,13 +4169,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,10 +4189,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>30</v>
@@ -4215,30 +4209,30 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>9</v>
@@ -4255,10 +4249,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>9</v>
@@ -4275,10 +4269,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>9</v>
@@ -4295,13 +4289,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,10 +4309,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>39</v>
@@ -4326,19 +4320,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>39</v>
@@ -4355,10 +4349,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>39</v>
@@ -4375,13 +4369,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,13 +4389,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,10 +4409,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>39</v>
@@ -4435,10 +4429,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>39</v>
@@ -4446,19 +4440,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>39</v>
@@ -4475,10 +4469,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>39</v>
@@ -4495,10 +4489,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>39</v>
@@ -4515,13 +4509,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,13 +4529,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,10 +4549,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>39</v>
@@ -4566,19 +4560,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>39</v>
@@ -4595,13 +4589,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,13 +4609,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,10 +4629,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>39</v>
@@ -4655,10 +4649,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>39</v>
@@ -4666,19 +4660,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>39</v>
@@ -4695,10 +4689,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>39</v>
@@ -4715,10 +4709,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>39</v>
@@ -4735,10 +4729,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>39</v>
@@ -4755,10 +4749,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>39</v>
@@ -4766,19 +4760,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>39</v>
@@ -4795,13 +4789,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,10 +4809,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>30</v>
@@ -4835,13 +4829,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,33 +4849,33 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,10 +4889,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>39</v>
@@ -4915,13 +4909,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,13 +4929,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,13 +4949,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,10 +4969,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>39</v>
@@ -4995,30 +4989,30 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>30</v>
@@ -5035,10 +5029,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>30</v>
@@ -5055,13 +5049,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5075,13 +5069,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,13 +5089,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,10 +5109,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>30</v>
@@ -5135,30 +5129,30 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>39</v>
@@ -5175,13 +5169,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,10 +5189,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5215,13 +5209,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,13 +5229,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,30 +5249,30 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -5295,10 +5289,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5315,10 +5309,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>9</v>
@@ -5335,10 +5329,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>9</v>
@@ -5355,13 +5349,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5375,33 +5369,33 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,13 +5409,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,10 +5429,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>30</v>
@@ -5455,10 +5449,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>30</v>
@@ -5475,10 +5469,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>30</v>
@@ -5495,30 +5489,30 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>39</v>
@@ -5535,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>39</v>
@@ -5555,10 +5549,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>39</v>
@@ -5575,10 +5569,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>39</v>
@@ -5595,10 +5589,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>39</v>
@@ -5615,10 +5609,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>39</v>
@@ -5635,10 +5629,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>39</v>
@@ -5655,10 +5649,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>39</v>
@@ -5675,10 +5669,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>39</v>
@@ -5686,19 +5680,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>39</v>
@@ -5715,13 +5709,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,13 +5729,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,10 +5749,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>9</v>
@@ -5775,13 +5769,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,10 +5789,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>39</v>
@@ -5815,10 +5809,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>39</v>
@@ -5835,10 +5829,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>39</v>
@@ -5846,19 +5840,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>39</v>
@@ -5875,10 +5869,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>39</v>
@@ -5895,10 +5889,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>39</v>
@@ -5915,10 +5909,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>39</v>
@@ -5935,10 +5929,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>39</v>
@@ -5955,10 +5949,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>39</v>
@@ -5975,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>39</v>
@@ -5986,19 +5980,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>39</v>
@@ -6015,10 +6009,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>39</v>
@@ -6035,10 +6029,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>39</v>
@@ -6055,13 +6049,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6075,13 +6069,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6095,10 +6089,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>39</v>
@@ -6106,19 +6100,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>39</v>
@@ -6135,10 +6129,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>39</v>
@@ -6155,10 +6149,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>39</v>
@@ -6175,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>39</v>
@@ -6195,10 +6189,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>39</v>
@@ -6215,10 +6209,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>39</v>
@@ -6235,10 +6229,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>39</v>
@@ -6246,19 +6240,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>39</v>
@@ -6275,10 +6269,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>39</v>
@@ -6295,10 +6289,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>39</v>
@@ -6315,10 +6309,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>39</v>
@@ -6335,33 +6329,33 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,13 +6369,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6395,13 +6389,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6415,13 +6409,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6435,13 +6429,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,13 +6449,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,13 +6469,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,10 +6489,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>39</v>
@@ -6515,33 +6509,33 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6549,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,10 +6569,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>39</v>
@@ -6595,10 +6589,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>39</v>
@@ -6615,10 +6609,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>39</v>
@@ -6635,32 +6629,12 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F235" s="1" t="s">
         <v>39</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -694,7 +694,7 @@
     <t>20098166</t>
   </si>
   <si>
-    <t>HAPPYTOS JG.BKR 140</t>
+    <t>HAPPYTOS J.BKR 140 G</t>
   </si>
   <si>
     <t>20072195</t>
@@ -727,13 +727,13 @@
     <t>10036957</t>
   </si>
   <si>
-    <t>HAPPYTOS CHIP HJU140</t>
+    <t>HAPPYTOS HIJAU 140 G</t>
   </si>
   <si>
     <t>20070033</t>
   </si>
   <si>
-    <t>HAPPYTOS NC.CHS 140G</t>
+    <t>HAPPYTOS N.CHS 140 G</t>
   </si>
   <si>
     <t>20116112</t>
@@ -1189,7 +1189,7 @@
     <t>20069696</t>
   </si>
   <si>
-    <t>OISHI POPCRN KRML100</t>
+    <t>OISHI PPCR KRM 100 G</t>
   </si>
   <si>
     <t>31</t>
@@ -1198,13 +1198,13 @@
     <t>20069844</t>
   </si>
   <si>
-    <t>OISHI POPCRN COK 100</t>
+    <t>OISHI PPCR COK 100 G</t>
   </si>
   <si>
     <t>20125388</t>
   </si>
   <si>
-    <t>OISHI PCORN M/BLG100</t>
+    <t>OISHI PPCR M/B 100 G</t>
   </si>
   <si>
     <t>20045784</t>
@@ -1357,7 +1357,7 @@
     <t>10000348</t>
   </si>
   <si>
-    <t>DK KACANG 180G</t>
+    <t>DK KACANG GARING160</t>
   </si>
   <si>
     <t>10003381</t>
@@ -1480,7 +1480,7 @@
     <t>20104000</t>
   </si>
   <si>
-    <t>IDM KACANG ALMOND 65</t>
+    <t>IDM KCG ALMD 65 G</t>
   </si>
   <si>
     <t>20139150</t>
@@ -2372,7 +2372,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -2972,7 +2972,7 @@
         <v>79</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>9</v>
@@ -2992,7 +2992,7 @@
         <v>79</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>9</v>
@@ -3372,7 +3372,7 @@
         <v>160</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>30</v>
@@ -3392,7 +3392,7 @@
         <v>160</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>39</v>
@@ -3412,7 +3412,7 @@
         <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>30</v>
@@ -3432,7 +3432,7 @@
         <v>160</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -6232,7 +6232,7 @@
         <v>472</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>39</v>
@@ -6252,7 +6252,7 @@
         <v>472</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>39</v>
@@ -6272,7 +6272,7 @@
         <v>472</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>39</v>
@@ -6292,7 +6292,7 @@
         <v>472</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>39</v>
@@ -6312,7 +6312,7 @@
         <v>472</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>39</v>
@@ -6332,7 +6332,7 @@
         <v>483</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>83</v>
@@ -6352,7 +6352,7 @@
         <v>483</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>83</v>
@@ -6372,7 +6372,7 @@
         <v>483</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>83</v>
@@ -6392,7 +6392,7 @@
         <v>483</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>83</v>
@@ -6412,7 +6412,7 @@
         <v>483</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>83</v>
@@ -6432,7 +6432,7 @@
         <v>483</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>30</v>
@@ -6452,7 +6452,7 @@
         <v>483</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>83</v>
@@ -6472,7 +6472,7 @@
         <v>483</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>39</v>
@@ -6492,7 +6492,7 @@
         <v>483</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>39</v>
